--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/10.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/10.xlsx
@@ -426,13 +426,13 @@
         <v>-6.611486598214277</v>
       </c>
       <c r="E2">
-        <v>-6.562988130278028</v>
+        <v>-3.821776016162946</v>
       </c>
       <c r="F2">
-        <v>-4.42545939118735</v>
+        <v>-4.416624852836494</v>
       </c>
       <c r="G2">
-        <v>-9.891209386356316</v>
+        <v>-8.958936588678775</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.831336721578198</v>
       </c>
       <c r="E3">
-        <v>-6.472350723014507</v>
+        <v>-4.343157342562066</v>
       </c>
       <c r="F3">
-        <v>-4.732525246996294</v>
+        <v>-4.21191290168486</v>
       </c>
       <c r="G3">
-        <v>-10.18966168781269</v>
+        <v>-8.544207996246577</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.281287114675182</v>
       </c>
       <c r="E4">
-        <v>-6.486547489028553</v>
+        <v>-4.579670483034673</v>
       </c>
       <c r="F4">
-        <v>-4.505814342728513</v>
+        <v>-4.35563050423356</v>
       </c>
       <c r="G4">
-        <v>-8.327979714349079</v>
+        <v>-8.563323086190328</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.72903703710745</v>
       </c>
       <c r="E5">
-        <v>-7.081344436040023</v>
+        <v>-5.492574615188955</v>
       </c>
       <c r="F5">
-        <v>-4.296493355347703</v>
+        <v>-4.005419132249805</v>
       </c>
       <c r="G5">
-        <v>-9.585000476701428</v>
+        <v>-8.519186893060764</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.13701490883729</v>
       </c>
       <c r="E6">
-        <v>-8.684111770048801</v>
+        <v>-6.521928456450482</v>
       </c>
       <c r="F6">
-        <v>-4.277890708583035</v>
+        <v>-3.696353597530504</v>
       </c>
       <c r="G6">
-        <v>-9.754848015593735</v>
+        <v>-8.789946481081136</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.38323926027029</v>
       </c>
       <c r="E7">
-        <v>-9.778449213320396</v>
+        <v>-7.87937929651574</v>
       </c>
       <c r="F7">
-        <v>-4.619652733058236</v>
+        <v>-3.975713877185414</v>
       </c>
       <c r="G7">
-        <v>-9.752000946429963</v>
+        <v>-8.415450948587702</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.38328927810813</v>
       </c>
       <c r="E8">
-        <v>-10.77875289382272</v>
+        <v>-7.996915839384824</v>
       </c>
       <c r="F8">
-        <v>-4.283994119606862</v>
+        <v>-4.043883544231397</v>
       </c>
       <c r="G8">
-        <v>-9.845825117558446</v>
+        <v>-7.931720655480475</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.03698852557826</v>
       </c>
       <c r="E9">
-        <v>-11.37752584101292</v>
+        <v>-8.698168153368609</v>
       </c>
       <c r="F9">
-        <v>-4.307788973252277</v>
+        <v>-3.723235776486153</v>
       </c>
       <c r="G9">
-        <v>-9.467906480977405</v>
+        <v>-8.016066734730027</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.26977265583621</v>
       </c>
       <c r="E10">
-        <v>-11.64379558418993</v>
+        <v>-8.614758190621329</v>
       </c>
       <c r="F10">
-        <v>-4.063574665763344</v>
+        <v>-3.899837079823786</v>
       </c>
       <c r="G10">
-        <v>-8.842474907152752</v>
+        <v>-8.201076572192196</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.02891753145073</v>
       </c>
       <c r="E11">
-        <v>-12.34783743816244</v>
+        <v>-10.199158034055</v>
       </c>
       <c r="F11">
-        <v>-3.820320436094255</v>
+        <v>-3.297680247380769</v>
       </c>
       <c r="G11">
-        <v>-8.47005508671244</v>
+        <v>-8.085326657957118</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.29867994490065</v>
       </c>
       <c r="E12">
-        <v>-11.62327706846118</v>
+        <v>-10.48762635681761</v>
       </c>
       <c r="F12">
-        <v>-3.984920352500128</v>
+        <v>-3.607074643958982</v>
       </c>
       <c r="G12">
-        <v>-8.13669639308999</v>
+        <v>-7.257865732052903</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.09071319972898</v>
       </c>
       <c r="E13">
-        <v>-13.29346432349615</v>
+        <v>-10.86444973594387</v>
       </c>
       <c r="F13">
-        <v>-3.684129379767391</v>
+        <v>-3.0130358120634</v>
       </c>
       <c r="G13">
-        <v>-8.505272670159208</v>
+        <v>-7.287693747361736</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.46269610453779</v>
       </c>
       <c r="E14">
-        <v>-13.88496454143004</v>
+        <v>-11.51196717735264</v>
       </c>
       <c r="F14">
-        <v>-3.443683315593793</v>
+        <v>-3.350428198488833</v>
       </c>
       <c r="G14">
-        <v>-7.596782831635791</v>
+        <v>-6.810250180233585</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.499393474001529</v>
       </c>
       <c r="E15">
-        <v>-13.65717777037021</v>
+        <v>-12.88828816860786</v>
       </c>
       <c r="F15">
-        <v>-3.603897026601842</v>
+        <v>-3.279218423074576</v>
       </c>
       <c r="G15">
-        <v>-8.111953375729476</v>
+        <v>-6.542675337021992</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.303648667763467</v>
       </c>
       <c r="E16">
-        <v>-15.66642093130748</v>
+        <v>-13.50589956766997</v>
       </c>
       <c r="F16">
-        <v>-3.027913290617679</v>
+        <v>-2.646064910786205</v>
       </c>
       <c r="G16">
-        <v>-7.888574315467153</v>
+        <v>-5.662934275961605</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.003324071610757</v>
       </c>
       <c r="E17">
-        <v>-15.53882664766736</v>
+        <v>-13.92760465268626</v>
       </c>
       <c r="F17">
-        <v>-3.139196995877167</v>
+        <v>-2.574951225990673</v>
       </c>
       <c r="G17">
-        <v>-6.552686426732747</v>
+        <v>-5.520478190861227</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.728506164665303</v>
       </c>
       <c r="E18">
-        <v>-16.44400973163857</v>
+        <v>-15.19558190330797</v>
       </c>
       <c r="F18">
-        <v>-2.834598846561164</v>
+        <v>-2.309637572385034</v>
       </c>
       <c r="G18">
-        <v>-6.198156794386657</v>
+        <v>-4.751905249009567</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.5975473118700513</v>
       </c>
       <c r="E19">
-        <v>-18.28087200099985</v>
+        <v>-15.62796965850835</v>
       </c>
       <c r="F19">
-        <v>-2.213473228961441</v>
+        <v>-2.206067624380414</v>
       </c>
       <c r="G19">
-        <v>-5.147177765307469</v>
+        <v>-5.050046359185252</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.275155126170026</v>
       </c>
       <c r="E20">
-        <v>-17.26052982301359</v>
+        <v>-16.10904756623921</v>
       </c>
       <c r="F20">
-        <v>-2.301092134257753</v>
+        <v>-1.834367573600637</v>
       </c>
       <c r="G20">
-        <v>-5.634619179964219</v>
+        <v>-4.696754870870849</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.800376918435134</v>
       </c>
       <c r="E21">
-        <v>-19.69311284808392</v>
+        <v>-16.48286403862438</v>
       </c>
       <c r="F21">
-        <v>-1.989562206515124</v>
+        <v>-1.734784557905691</v>
       </c>
       <c r="G21">
-        <v>-5.752934766992232</v>
+        <v>-3.713360628975882</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.925173079636183</v>
       </c>
       <c r="E22">
-        <v>-19.5505247870044</v>
+        <v>-16.87462232502794</v>
       </c>
       <c r="F22">
-        <v>-1.727903309890636</v>
+        <v>-1.315330783089328</v>
       </c>
       <c r="G22">
-        <v>-4.993300298096605</v>
+        <v>-3.695261876512686</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.619991995811385</v>
       </c>
       <c r="E23">
-        <v>-20.00689081207539</v>
+        <v>-17.4609691395411</v>
       </c>
       <c r="F23">
-        <v>-1.516559449312189</v>
+        <v>-1.170358203925386</v>
       </c>
       <c r="G23">
-        <v>-4.311413991190761</v>
+        <v>-3.789370754557548</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.887314756005717</v>
       </c>
       <c r="E24">
-        <v>-20.41661355486739</v>
+        <v>-19.0392510145904</v>
       </c>
       <c r="F24">
-        <v>-1.335697852421959</v>
+        <v>-0.8231554623485989</v>
       </c>
       <c r="G24">
-        <v>-5.375830524613851</v>
+        <v>-3.29529169609456</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.760061574557488</v>
       </c>
       <c r="E25">
-        <v>-20.40330889823285</v>
+        <v>-18.54107811748059</v>
       </c>
       <c r="F25">
-        <v>-0.7610618702021508</v>
+        <v>-0.7187206987754569</v>
       </c>
       <c r="G25">
-        <v>-4.856078185493814</v>
+        <v>-3.436324246613051</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.284514685284857</v>
       </c>
       <c r="E26">
-        <v>-21.93123414231686</v>
+        <v>-18.52370689118717</v>
       </c>
       <c r="F26">
-        <v>-0.663310374834795</v>
+        <v>-0.657770253644872</v>
       </c>
       <c r="G26">
-        <v>-4.435195288904111</v>
+        <v>-4.07335266146177</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.517641082401604</v>
       </c>
       <c r="E27">
-        <v>-20.93219390606268</v>
+        <v>-19.35519358915755</v>
       </c>
       <c r="F27">
-        <v>-1.121723096972222</v>
+        <v>-0.53986623610221</v>
       </c>
       <c r="G27">
-        <v>-5.548617827945032</v>
+        <v>-3.630418221034982</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.522979565402717</v>
       </c>
       <c r="E28">
-        <v>-21.61429077499402</v>
+        <v>-19.24800008092198</v>
       </c>
       <c r="F28">
-        <v>-0.8505561992984009</v>
+        <v>-0.5094601822150513</v>
       </c>
       <c r="G28">
-        <v>-5.586887734379007</v>
+        <v>-4.268913207557597</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.365595408682258</v>
       </c>
       <c r="E29">
-        <v>-20.98907606807303</v>
+        <v>-18.18813791027078</v>
       </c>
       <c r="F29">
-        <v>-0.7245780846806521</v>
+        <v>-0.5749964692875342</v>
       </c>
       <c r="G29">
-        <v>-4.985441062986375</v>
+        <v>-4.283138621739845</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.1086323801752644</v>
       </c>
       <c r="E30">
-        <v>-21.54779013419138</v>
+        <v>-18.6103320704799</v>
       </c>
       <c r="F30">
-        <v>-0.6770099149422933</v>
+        <v>-0.3197590767695477</v>
       </c>
       <c r="G30">
-        <v>-6.036214838242128</v>
+        <v>-4.940291842921795</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.192303088464722</v>
       </c>
       <c r="E31">
-        <v>-20.92205918123351</v>
+        <v>-18.29916250751683</v>
       </c>
       <c r="F31">
-        <v>-0.9089801238504472</v>
+        <v>-0.7068385967497007</v>
       </c>
       <c r="G31">
-        <v>-6.447394525856227</v>
+        <v>-3.993399676142832</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.483852488952226</v>
       </c>
       <c r="E32">
-        <v>-20.4005646429842</v>
+        <v>-18.92711241273846</v>
       </c>
       <c r="F32">
-        <v>-1.317905348977229</v>
+        <v>-0.6845853348408948</v>
       </c>
       <c r="G32">
-        <v>-6.424389544903832</v>
+        <v>-4.336269567099609</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.716505420649914</v>
       </c>
       <c r="E33">
-        <v>-20.23015816607557</v>
+        <v>-18.08941264842956</v>
       </c>
       <c r="F33">
-        <v>-0.7834360737517654</v>
+        <v>-0.5106546880098882</v>
       </c>
       <c r="G33">
-        <v>-5.487650821293814</v>
+        <v>-4.917750338344897</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.850254322278952</v>
       </c>
       <c r="E34">
-        <v>-20.17030985359019</v>
+        <v>-17.7375094617675</v>
       </c>
       <c r="F34">
-        <v>-1.166105365679414</v>
+        <v>-0.8514384105823823</v>
       </c>
       <c r="G34">
-        <v>-6.156016860217274</v>
+        <v>-3.352974641570821</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.845580229691729</v>
       </c>
       <c r="E35">
-        <v>-20.377419612331</v>
+        <v>-17.96552718500172</v>
       </c>
       <c r="F35">
-        <v>-1.281661790002542</v>
+        <v>-0.7260799147819276</v>
       </c>
       <c r="G35">
-        <v>-5.653472736810368</v>
+        <v>-4.953553888352115</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.667346286655338</v>
       </c>
       <c r="E36">
-        <v>-18.63856710591772</v>
+        <v>-17.14459183146921</v>
       </c>
       <c r="F36">
-        <v>-1.079835870882262</v>
+        <v>-1.166313285897516</v>
       </c>
       <c r="G36">
-        <v>-6.164091280787556</v>
+        <v>-4.757956926255355</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.292290433016724</v>
       </c>
       <c r="E37">
-        <v>-20.19542477043673</v>
+        <v>-16.84193127116657</v>
       </c>
       <c r="F37">
-        <v>-1.729380288969827</v>
+        <v>-0.621932594697557</v>
       </c>
       <c r="G37">
-        <v>-5.97856499822126</v>
+        <v>-4.452645174441609</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.702831534980081</v>
       </c>
       <c r="E38">
-        <v>-19.01018273993516</v>
+        <v>-16.44486108475201</v>
       </c>
       <c r="F38">
-        <v>-1.743907368112722</v>
+        <v>-1.226926585495162</v>
       </c>
       <c r="G38">
-        <v>-4.922908168295081</v>
+        <v>-4.532627954670401</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.891314268777777</v>
       </c>
       <c r="E39">
-        <v>-19.10139526339766</v>
+        <v>-15.66119507230263</v>
       </c>
       <c r="F39">
-        <v>-1.04650236659361</v>
+        <v>-1.121274950207307</v>
       </c>
       <c r="G39">
-        <v>-5.369510693179382</v>
+        <v>-3.510573161967825</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.864617374669011</v>
       </c>
       <c r="E40">
-        <v>-18.4869447391929</v>
+        <v>-15.738754246632</v>
       </c>
       <c r="F40">
-        <v>-1.250004072969753</v>
+        <v>-1.287244157930008</v>
       </c>
       <c r="G40">
-        <v>-3.90501142078983</v>
+        <v>-4.104905470996564</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.636935905402906</v>
       </c>
       <c r="E41">
-        <v>-17.92272857715523</v>
+        <v>-14.91090391328978</v>
       </c>
       <c r="F41">
-        <v>-1.421447132490153</v>
+        <v>-1.216400520907789</v>
       </c>
       <c r="G41">
-        <v>-4.076901566279869</v>
+        <v>-3.059226625325749</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.230946893897873</v>
       </c>
       <c r="E42">
-        <v>-18.06296183175075</v>
+        <v>-13.63611130928653</v>
       </c>
       <c r="F42">
-        <v>-1.807752957316091</v>
+        <v>-1.095065405582731</v>
       </c>
       <c r="G42">
-        <v>-5.433784934824333</v>
+        <v>-3.659895318516652</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.677648301848395</v>
       </c>
       <c r="E43">
-        <v>-16.06552893102549</v>
+        <v>-14.64792184224234</v>
       </c>
       <c r="F43">
-        <v>-1.239234468365957</v>
+        <v>-1.647632023457155</v>
       </c>
       <c r="G43">
-        <v>-4.457491813111102</v>
+        <v>-3.321656880769315</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.011913205589121</v>
       </c>
       <c r="E44">
-        <v>-16.29642676372859</v>
+        <v>-13.01522582351687</v>
       </c>
       <c r="F44">
-        <v>-1.831655498723871</v>
+        <v>-1.533113543489735</v>
       </c>
       <c r="G44">
-        <v>-3.054416402657188</v>
+        <v>-3.1020551529673</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.275920111711085</v>
       </c>
       <c r="E45">
-        <v>-15.72309025503947</v>
+        <v>-12.99555413242755</v>
       </c>
       <c r="F45">
-        <v>-1.902705399229387</v>
+        <v>-1.463176968773581</v>
       </c>
       <c r="G45">
-        <v>-3.97900873468362</v>
+        <v>-2.908881510205287</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.516640779039598</v>
       </c>
       <c r="E46">
-        <v>-15.73481900271933</v>
+        <v>-12.48197989521765</v>
       </c>
       <c r="F46">
-        <v>-2.344193746960217</v>
+        <v>-1.838819220023281</v>
       </c>
       <c r="G46">
-        <v>-3.82234047758315</v>
+        <v>-2.235840980980376</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.780091689241117</v>
       </c>
       <c r="E47">
-        <v>-15.63743416918438</v>
+        <v>-12.76090219477209</v>
       </c>
       <c r="F47">
-        <v>-2.036834649090683</v>
+        <v>-1.959179346915244</v>
       </c>
       <c r="G47">
-        <v>-3.740652766401634</v>
+        <v>-2.418861180573444</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.113705574096993</v>
       </c>
       <c r="E48">
-        <v>-15.44149162734649</v>
+        <v>-11.72044906371777</v>
       </c>
       <c r="F48">
-        <v>-2.211001380631488</v>
+        <v>-2.031535582814975</v>
       </c>
       <c r="G48">
-        <v>-3.406744522219663</v>
+        <v>-2.995005352409427</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.560939885276122</v>
       </c>
       <c r="E49">
-        <v>-14.05872661757836</v>
+        <v>-11.76886297933377</v>
       </c>
       <c r="F49">
-        <v>-2.127868913188738</v>
+        <v>-2.197349885833352</v>
       </c>
       <c r="G49">
-        <v>-4.444680001874123</v>
+        <v>-2.218831397999601</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.153357550433826</v>
       </c>
       <c r="E50">
-        <v>-13.58949066937756</v>
+        <v>-11.08965074834532</v>
       </c>
       <c r="F50">
-        <v>-2.371382421854903</v>
+        <v>-2.120344023701707</v>
       </c>
       <c r="G50">
-        <v>-3.956089827915245</v>
+        <v>-2.556103156449471</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.914649635451505</v>
       </c>
       <c r="E51">
-        <v>-13.02107208346077</v>
+        <v>-10.65340020481639</v>
       </c>
       <c r="F51">
-        <v>-2.087081759009696</v>
+        <v>-2.185655823208031</v>
       </c>
       <c r="G51">
-        <v>-3.656842995529444</v>
+        <v>-2.412812813873196</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.857488508632568</v>
       </c>
       <c r="E52">
-        <v>-13.09426128037274</v>
+        <v>-10.85972653755387</v>
       </c>
       <c r="F52">
-        <v>-2.112300576220524</v>
+        <v>-2.360306321312071</v>
       </c>
       <c r="G52">
-        <v>-3.666407161592399</v>
+        <v>-2.261643372913456</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.977594857541182</v>
       </c>
       <c r="E53">
-        <v>-12.95955729254058</v>
+        <v>-10.05091843741391</v>
       </c>
       <c r="F53">
-        <v>-3.039180744030558</v>
+        <v>-2.635301933121631</v>
       </c>
       <c r="G53">
-        <v>-4.674892028129502</v>
+        <v>-1.594025517281871</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.261152386099351</v>
       </c>
       <c r="E54">
-        <v>-12.65826885986225</v>
+        <v>-9.601426635886554</v>
       </c>
       <c r="F54">
-        <v>-2.48901887672646</v>
+        <v>-2.262935874950003</v>
       </c>
       <c r="G54">
-        <v>-3.325242201588346</v>
+        <v>-2.441061698959797</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.686388549697406</v>
       </c>
       <c r="E55">
-        <v>-13.26325487339098</v>
+        <v>-8.298906185534337</v>
       </c>
       <c r="F55">
-        <v>-2.767391742437235</v>
+        <v>-2.574378824115338</v>
       </c>
       <c r="G55">
-        <v>-3.544440042834569</v>
+        <v>-2.823542267293954</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.219688899824856</v>
       </c>
       <c r="E56">
-        <v>-12.30579961394924</v>
+        <v>-8.817964404767521</v>
       </c>
       <c r="F56">
-        <v>-2.600892379576742</v>
+        <v>-2.811905721561471</v>
       </c>
       <c r="G56">
-        <v>-4.032255549137258</v>
+        <v>-2.470293816071562</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.823566379486161</v>
       </c>
       <c r="E57">
-        <v>-11.98477609154549</v>
+        <v>-7.794991183382803</v>
       </c>
       <c r="F57">
-        <v>-2.966734216083922</v>
+        <v>-2.775937180564514</v>
       </c>
       <c r="G57">
-        <v>-4.075007934231405</v>
+        <v>-2.317369785976008</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.461826287475716</v>
       </c>
       <c r="E58">
-        <v>-11.97681503424</v>
+        <v>-8.100024664065471</v>
       </c>
       <c r="F58">
-        <v>-2.364950148972165</v>
+        <v>-2.996154512761749</v>
       </c>
       <c r="G58">
-        <v>-4.430100359319172</v>
+        <v>-2.327039889496219</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.097939178900133</v>
       </c>
       <c r="E59">
-        <v>-11.61107735948451</v>
+        <v>-8.097828354171751</v>
       </c>
       <c r="F59">
-        <v>-2.516161991413992</v>
+        <v>-2.98422436542663</v>
       </c>
       <c r="G59">
-        <v>-5.022539036299448</v>
+        <v>-2.7731855590961</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.701036315799314</v>
       </c>
       <c r="E60">
-        <v>-11.67935316209816</v>
+        <v>-7.512803854068832</v>
       </c>
       <c r="F60">
-        <v>-2.972754790367468</v>
+        <v>-3.261942820889193</v>
       </c>
       <c r="G60">
-        <v>-4.401967343326446</v>
+        <v>-2.613451736826266</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.248716629350754</v>
       </c>
       <c r="E61">
-        <v>-10.51717012124365</v>
+        <v>-7.296596391046619</v>
       </c>
       <c r="F61">
-        <v>-3.209792122678547</v>
+        <v>-3.255556108213608</v>
       </c>
       <c r="G61">
-        <v>-4.430984274978158</v>
+        <v>-3.400874924978535</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.721568180273896</v>
       </c>
       <c r="E62">
-        <v>-10.00247282247985</v>
+        <v>-7.277635670376503</v>
       </c>
       <c r="F62">
-        <v>-3.103331172438157</v>
+        <v>-2.895782891299338</v>
       </c>
       <c r="G62">
-        <v>-4.11827676442968</v>
+        <v>-2.905478269390916</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.106218429728348</v>
       </c>
       <c r="E63">
-        <v>-9.556467945938403</v>
+        <v>-6.884935461379345</v>
       </c>
       <c r="F63">
-        <v>-3.283369372130005</v>
+        <v>-3.013903112734131</v>
       </c>
       <c r="G63">
-        <v>-4.312052926479841</v>
+        <v>-3.096010096812591</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.399277741616811</v>
       </c>
       <c r="E64">
-        <v>-9.99183996550984</v>
+        <v>-6.876213620440572</v>
       </c>
       <c r="F64">
-        <v>-3.180694889287811</v>
+        <v>-3.120417906855703</v>
       </c>
       <c r="G64">
-        <v>-4.705935013651247</v>
+        <v>-3.656478835520125</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.600135803026161</v>
       </c>
       <c r="E65">
-        <v>-9.680172270405935</v>
+        <v>-7.352695127053639</v>
       </c>
       <c r="F65">
-        <v>-3.306481651035514</v>
+        <v>-3.389667962359446</v>
       </c>
       <c r="G65">
-        <v>-4.894758599574659</v>
+        <v>-3.253625169937292</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.711625814328055</v>
       </c>
       <c r="E66">
-        <v>-11.0504386919129</v>
+        <v>-7.000755712599522</v>
       </c>
       <c r="F66">
-        <v>-3.275599285891745</v>
+        <v>-3.1525221139186</v>
       </c>
       <c r="G66">
-        <v>-5.113291021167488</v>
+        <v>-3.588430571960405</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.742008174389426</v>
       </c>
       <c r="E67">
-        <v>-9.883654721466595</v>
+        <v>-5.877368108568721</v>
       </c>
       <c r="F67">
-        <v>-3.152818669448803</v>
+        <v>-3.55548143701042</v>
       </c>
       <c r="G67">
-        <v>-4.567266192647796</v>
+        <v>-3.129506196578937</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.698003279375818</v>
       </c>
       <c r="E68">
-        <v>-10.20641717788929</v>
+        <v>-6.580572194849813</v>
       </c>
       <c r="F68">
-        <v>-3.223824666481971</v>
+        <v>-3.396575718131391</v>
       </c>
       <c r="G68">
-        <v>-4.916618131770466</v>
+        <v>-2.974400516973003</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.586397989767316</v>
       </c>
       <c r="E69">
-        <v>-10.05011689751455</v>
+        <v>-6.206488542498187</v>
       </c>
       <c r="F69">
-        <v>-3.722513440110912</v>
+        <v>-3.451922257782037</v>
       </c>
       <c r="G69">
-        <v>-4.977475890418888</v>
+        <v>-3.08506543325976</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.414359945170354</v>
       </c>
       <c r="E70">
-        <v>-10.7313352424884</v>
+        <v>-5.798726628951518</v>
       </c>
       <c r="F70">
-        <v>-3.459121598879767</v>
+        <v>-3.31328917435172</v>
       </c>
       <c r="G70">
-        <v>-4.700379918236351</v>
+        <v>-2.837770992021742</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.184492769193577</v>
       </c>
       <c r="E71">
-        <v>-9.243020560549484</v>
+        <v>-7.012375776903204</v>
       </c>
       <c r="F71">
-        <v>-3.358208225135926</v>
+        <v>-3.8685943748598</v>
       </c>
       <c r="G71">
-        <v>-4.829047581165665</v>
+        <v>-3.053323922629228</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.901456048383642</v>
       </c>
       <c r="E72">
-        <v>-9.697824262087833</v>
+        <v>-6.019136515852849</v>
       </c>
       <c r="F72">
-        <v>-2.869746475461947</v>
+        <v>-3.775955563102522</v>
       </c>
       <c r="G72">
-        <v>-4.834039883838885</v>
+        <v>-2.791727924661558</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.574262254486527</v>
       </c>
       <c r="E73">
-        <v>-10.08347363705505</v>
+        <v>-6.26685762949444</v>
       </c>
       <c r="F73">
-        <v>-3.378708661620408</v>
+        <v>-3.855623798066765</v>
       </c>
       <c r="G73">
-        <v>-4.12082257394938</v>
+        <v>-2.556364689547073</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.211235936648229</v>
       </c>
       <c r="E74">
-        <v>-10.3433310610372</v>
+        <v>-7.151241432348415</v>
       </c>
       <c r="F74">
-        <v>-4.038720330209748</v>
+        <v>-4.027480212921161</v>
       </c>
       <c r="G74">
-        <v>-4.298393615584808</v>
+        <v>-2.540487313140729</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.824231268366114</v>
       </c>
       <c r="E75">
-        <v>-9.844922683278989</v>
+        <v>-6.369821543006842</v>
       </c>
       <c r="F75">
-        <v>-3.858280372327543</v>
+        <v>-4.028543008298953</v>
       </c>
       <c r="G75">
-        <v>-4.50338259537648</v>
+        <v>-1.908653144243126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.426789776315743</v>
       </c>
       <c r="E76">
-        <v>-9.828701689383514</v>
+        <v>-7.033849800647577</v>
       </c>
       <c r="F76">
-        <v>-4.199574369220161</v>
+        <v>-4.117851783096977</v>
       </c>
       <c r="G76">
-        <v>-3.950908824146286</v>
+        <v>-1.990277955059397</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.028888396283156</v>
       </c>
       <c r="E77">
-        <v>-10.00709186596767</v>
+        <v>-7.533594078238047</v>
       </c>
       <c r="F77">
-        <v>-4.093270808786303</v>
+        <v>-4.198461871798202</v>
       </c>
       <c r="G77">
-        <v>-4.455661081427885</v>
+        <v>-1.564124669971174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.641085728531816</v>
       </c>
       <c r="E78">
-        <v>-11.48913008293196</v>
+        <v>-7.302302268296283</v>
       </c>
       <c r="F78">
-        <v>-4.126526446539093</v>
+        <v>-4.356926070851538</v>
       </c>
       <c r="G78">
-        <v>-3.994118064524853</v>
+        <v>-1.835526503826165</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.273757896435699</v>
       </c>
       <c r="E79">
-        <v>-11.56326120243752</v>
+        <v>-8.932937831348264</v>
       </c>
       <c r="F79">
-        <v>-4.269371778212645</v>
+        <v>-4.326704742895204</v>
       </c>
       <c r="G79">
-        <v>-3.355444308543117</v>
+        <v>-1.56831913116943</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.933603010077206</v>
       </c>
       <c r="E80">
-        <v>-12.37244063744611</v>
+        <v>-8.209097489014219</v>
       </c>
       <c r="F80">
-        <v>-4.242077900657804</v>
+        <v>-4.510478879573677</v>
       </c>
       <c r="G80">
-        <v>-3.330625148635201</v>
+        <v>-1.786345039294752</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.627784188021354</v>
       </c>
       <c r="E81">
-        <v>-12.64776280016446</v>
+        <v>-9.992451309500874</v>
       </c>
       <c r="F81">
-        <v>-4.006477785790582</v>
+        <v>-4.365189864061866</v>
       </c>
       <c r="G81">
-        <v>-3.44936448549224</v>
+        <v>-1.614521104715499</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.36350969638637</v>
       </c>
       <c r="E82">
-        <v>-13.20094759951944</v>
+        <v>-10.64169862798057</v>
       </c>
       <c r="F82">
-        <v>-4.087013321425556</v>
+        <v>-4.676028105023159</v>
       </c>
       <c r="G82">
-        <v>-2.734528318834031</v>
+        <v>-1.039873299463267</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.143726244450916</v>
       </c>
       <c r="E83">
-        <v>-14.75396511807996</v>
+        <v>-11.58641076156473</v>
       </c>
       <c r="F83">
-        <v>-4.103859829296289</v>
+        <v>-4.929490306196946</v>
       </c>
       <c r="G83">
-        <v>-3.233417599965581</v>
+        <v>-0.5596687373553637</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.968205814666398</v>
       </c>
       <c r="E84">
-        <v>-14.6997909835262</v>
+        <v>-12.60650387348057</v>
       </c>
       <c r="F84">
-        <v>-4.32530977218889</v>
+        <v>-4.816793406148282</v>
       </c>
       <c r="G84">
-        <v>-2.601825100892345</v>
+        <v>-0.7132085289212221</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.832780705310094</v>
       </c>
       <c r="E85">
-        <v>-16.97243283511961</v>
+        <v>-13.80486036470836</v>
       </c>
       <c r="F85">
-        <v>-4.724513277476416</v>
+        <v>-5.109485430783847</v>
       </c>
       <c r="G85">
-        <v>-2.535200371914513</v>
+        <v>-0.7792969495216928</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.728218074888423</v>
       </c>
       <c r="E86">
-        <v>-17.39735313668134</v>
+        <v>-14.37282157475037</v>
       </c>
       <c r="F86">
-        <v>-4.584736218662833</v>
+        <v>-5.308070776624376</v>
       </c>
       <c r="G86">
-        <v>-2.487664248516118</v>
+        <v>-0.6323385224879056</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.645405401750381</v>
       </c>
       <c r="E87">
-        <v>-18.32987914671086</v>
+        <v>-16.31368477817182</v>
       </c>
       <c r="F87">
-        <v>-4.891420197099086</v>
+        <v>-5.044784138053386</v>
       </c>
       <c r="G87">
-        <v>-2.917919299527497</v>
+        <v>-0.2596306845856768</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.579157130521862</v>
       </c>
       <c r="E88">
-        <v>-18.97787660636444</v>
+        <v>-17.02031239080271</v>
       </c>
       <c r="F88">
-        <v>-4.640561554672297</v>
+        <v>-5.295612959253674</v>
       </c>
       <c r="G88">
-        <v>-2.418887664937759</v>
+        <v>0.3981482297031939</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.526967262018275</v>
       </c>
       <c r="E89">
-        <v>-21.27933766654267</v>
+        <v>-17.92297311475164</v>
       </c>
       <c r="F89">
-        <v>-5.373940067392784</v>
+        <v>-5.450440625408722</v>
       </c>
       <c r="G89">
-        <v>-3.280066497159451</v>
+        <v>-0.3599302827889759</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.487645799153249</v>
       </c>
       <c r="E90">
-        <v>-22.28470418098557</v>
+        <v>-19.90782138620959</v>
       </c>
       <c r="F90">
-        <v>-5.22466743304091</v>
+        <v>-5.439786992241316</v>
       </c>
       <c r="G90">
-        <v>-3.246610123939576</v>
+        <v>-0.2007062845321889</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.463632627858974</v>
       </c>
       <c r="E91">
-        <v>-25.14753752152465</v>
+        <v>-22.3774699710327</v>
       </c>
       <c r="F91">
-        <v>-5.050141190047291</v>
+        <v>-5.548957532256264</v>
       </c>
       <c r="G91">
-        <v>-2.622943070887356</v>
+        <v>-0.8461136901408032</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.462363762030208</v>
       </c>
       <c r="E92">
-        <v>-25.94692186725466</v>
+        <v>-24.324152263554</v>
       </c>
       <c r="F92">
-        <v>-5.035886643779917</v>
+        <v>-5.602962116714375</v>
       </c>
       <c r="G92">
-        <v>-2.269429776021822</v>
+        <v>-1.262249264427191</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.491847066514653</v>
       </c>
       <c r="E93">
-        <v>-28.32135022911848</v>
+        <v>-26.8495871196776</v>
       </c>
       <c r="F93">
-        <v>-5.454895585300977</v>
+        <v>-5.680838592986362</v>
       </c>
       <c r="G93">
-        <v>-2.763505523939271</v>
+        <v>-1.016490916319395</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.561970431379665</v>
       </c>
       <c r="E94">
-        <v>-30.60517741151084</v>
+        <v>-27.9014791760753</v>
       </c>
       <c r="F94">
-        <v>-5.498632555801388</v>
+        <v>-5.630014939355001</v>
       </c>
       <c r="G94">
-        <v>-2.97800239051973</v>
+        <v>-1.051516488124884</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.684383487888744</v>
       </c>
       <c r="E95">
-        <v>-31.51402403095425</v>
+        <v>-30.47953037169402</v>
       </c>
       <c r="F95">
-        <v>-5.274523553545801</v>
+        <v>-5.709934169642292</v>
       </c>
       <c r="G95">
-        <v>-4.433033502666967</v>
+        <v>-2.330469614674904</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.868785433250743</v>
       </c>
       <c r="E96">
-        <v>-34.64153988453065</v>
+        <v>-32.44744667883729</v>
       </c>
       <c r="F96">
-        <v>-5.619057295350769</v>
+        <v>-5.749583147009887</v>
       </c>
       <c r="G96">
-        <v>-3.843580937763114</v>
+        <v>-2.20983995631494</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.111458091276515</v>
       </c>
       <c r="E97">
-        <v>-37.47912924671398</v>
+        <v>-34.59640684833321</v>
       </c>
       <c r="F97">
-        <v>-5.342377612611317</v>
+        <v>-5.760110868332066</v>
       </c>
       <c r="G97">
-        <v>-4.787010273907999</v>
+        <v>-2.519707018790724</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.415892229765618</v>
       </c>
       <c r="E98">
-        <v>-38.94580235137024</v>
+        <v>-36.55776818935038</v>
       </c>
       <c r="F98">
-        <v>-5.571301914579378</v>
+        <v>-5.892454986440329</v>
       </c>
       <c r="G98">
-        <v>-5.987758383183816</v>
+        <v>-3.538755836143641</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.754553605931424</v>
       </c>
       <c r="E99">
-        <v>-41.26433575855739</v>
+        <v>-40.13199083293942</v>
       </c>
       <c r="F99">
-        <v>-6.084578238171618</v>
+        <v>-5.998837241777453</v>
       </c>
       <c r="G99">
-        <v>-5.267171798923892</v>
+        <v>-3.888173986177097</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.12690851907687</v>
       </c>
       <c r="E100">
-        <v>-43.28288493358042</v>
+        <v>-42.12616323237916</v>
       </c>
       <c r="F100">
-        <v>-5.649128688807196</v>
+        <v>-5.96117468944177</v>
       </c>
       <c r="G100">
-        <v>-5.814421529293115</v>
+        <v>-4.331237537879917</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.483905502596585</v>
       </c>
       <c r="E101">
-        <v>-45.75212369150583</v>
+        <v>-45.04510663011028</v>
       </c>
       <c r="F101">
-        <v>-5.505701843216879</v>
+        <v>-5.862362055431428</v>
       </c>
       <c r="G101">
-        <v>-5.65610130996855</v>
+        <v>-4.688339464110022</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.859530479827698</v>
       </c>
       <c r="E102">
-        <v>-48.07605503971012</v>
+        <v>-47.71626777980071</v>
       </c>
       <c r="F102">
-        <v>-5.544528251753495</v>
+        <v>-6.061740977243839</v>
       </c>
       <c r="G102">
-        <v>-6.230384955211462</v>
+        <v>-5.326566296443956</v>
       </c>
     </row>
   </sheetData>
